--- a/public/downloads/Import_cong_viec_CBQL.xlsx
+++ b/public/downloads/Import_cong_viec_CBQL.xlsx
@@ -524,13 +524,13 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="45" customWidth="1" min="2" max="3"/>
+    <col width="46" customWidth="1" min="2" max="3"/>
     <col width="48" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" style="7" min="4" max="5"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="11"/>
     <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="35" customWidth="1" min="8" max="8"/>
+    <col width="38" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="2">
@@ -621,17 +621,17 @@
       </c>
       <c r="B9" s="10" t="inlineStr">
         <is>
-          <t>Xây dựng và ban hành Kế hoạch giáo dục nhà trường, kế hoạch phát triển chiến lược năm học 2026 - 2027</t>
+          <t>Tổng hợp kết quả đánh giá, xếp loại chất lượng viên chức, người lao động cuối năm học 2025 - 2026 theo Nghị định 90/2020 &amp; 48/2023</t>
         </is>
       </c>
       <c r="C9" s="10" t="inlineStr">
         <is>
-          <t>N3_668 - Quyết định ban hành Kế hoạch nhiệm vụ, giải pháp trọng tâm năm học 2026 - 2027 của ngành Giáo dục tỉnh Cao Bằng</t>
+          <t>N2_1046 - Tham mưu công tác đánh giá, xếp loại</t>
         </is>
       </c>
       <c r="D9" s="9" t="inlineStr">
         <is>
-          <t>15/09/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
       <c r="E9" s="9" t="n">
@@ -645,7 +645,7 @@
       </c>
       <c r="H9" s="10" t="inlineStr">
         <is>
-          <t>Kế hoạch số 01/KH-THPT; Nghị quyết Hội đồng trường</t>
+          <t>Biên bản họp Hội đồng đánh giá xếp loại viên chức năm học 2025-2026</t>
         </is>
       </c>
     </row>
@@ -655,17 +655,17 @@
       </c>
       <c r="B10" s="10" t="inlineStr">
         <is>
-          <t>Phê duyệt kế hoạch giáo dục của các tổ chuyên môn, tổ văn phòng và các tổ chức đoàn thể trong nhà trường</t>
+          <t>Ban hành Quyết định công nhận kết quả đánh giá, xếp loại viên chức, người lao động và công khai toàn trường</t>
         </is>
       </c>
       <c r="C10" s="10" t="inlineStr">
         <is>
-          <t>N3_668 - Quyết định ban hành Kế hoạch nhiệm vụ, giải pháp trọng tâm năm học 2026 - 2027 của ngành Giáo dục tỉnh Cao Bằng</t>
+          <t>N2_1046 - Tham mưu công tác đánh giá, xếp loại</t>
         </is>
       </c>
       <c r="D10" s="9" t="inlineStr">
         <is>
-          <t>30/09/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="E10" s="9" t="n">
@@ -679,27 +679,27 @@
       </c>
       <c r="H10" s="10" t="inlineStr">
         <is>
-          <t>Kế hoạch năm học các tổ TN, XH, VP, Công đoàn, Đoàn TN</t>
+          <t>Quyết định số 85/QĐ-THPT công nhận kết quả xếp loại</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B11" s="10" t="inlineStr">
         <is>
-          <t>Chỉ đạo tổ chức Hội nghị cán bộ, viên chức, người lao động năm học 2026 - 2027</t>
+          <t>Chỉ đạo thẩm định hồ sơ thi đua, sáng kiến kinh nghiệm của CBGVNV đề nghị công nhận LĐTT, CSTĐ cơ sở năm học 2025 - 2026</t>
         </is>
       </c>
       <c r="C11" s="10" t="inlineStr">
         <is>
-          <t>N3_668 - Quyết định ban hành Kế hoạch nhiệm vụ, giải pháp trọng tâm năm học 2026 - 2027 của ngành Giáo dục tỉnh Cao Bằng</t>
+          <t>N1_576 - Tiếp nhận, thẩm định hồ sơ đề nghị xét tặng thưởng danh hiệu Lao động tiên tiến, Chiến sỹ thi đua cơ sở và hồ sơ trình khen thưở</t>
         </is>
       </c>
       <c r="D11" s="9" t="inlineStr">
         <is>
-          <t>15/10/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="E11" s="9" t="n">
@@ -713,27 +713,27 @@
       </c>
       <c r="H11" s="10" t="inlineStr">
         <is>
-          <t>Nghị quyết Hội nghị CBVC-NLĐ năm học 2026-2027</t>
+          <t>Biên bản thẩm định hồ sơ sáng kiến kinh nghiệm và thi đua</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B12" s="10" t="inlineStr">
         <is>
-          <t>Xây dựng lịch công tác tuần, tháng, quý và chương trình điều hành tổng thể hoạt động sư phạm nhà trường</t>
+          <t>Tổ chức họp Hội đồng Thi đua - Khen thưởng nhà trường xét duyệt danh hiệu và hoàn thiện tờ trình nộp Sở GD&amp;ĐT</t>
         </is>
       </c>
       <c r="C12" s="10" t="inlineStr">
         <is>
-          <t>N1_610 - Chủ trì xây dựng kế hoạch, chương trình công tác của Phòng</t>
+          <t>N1_576 - Tiếp nhận, thẩm định hồ sơ đề nghị xét tặng thưởng danh hiệu Lao động tiên tiến, Chiến sỹ thi đua cơ sở và hồ sơ trình khen thưở</t>
         </is>
       </c>
       <c r="D12" s="9" t="inlineStr">
         <is>
-          <t>31/05/2027</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="E12" s="9" t="n">
@@ -747,27 +747,27 @@
       </c>
       <c r="H12" s="10" t="inlineStr">
         <is>
-          <t>Lịch công tác tuần đưa lên website và bảng tin điện tử</t>
+          <t>Tờ trình số 28/TTr-THPT đề nghị khen thưởng năm học 2025-2026</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B13" s="10" t="inlineStr">
         <is>
-          <t>Phân công nhiệm vụ cụ thể cho các Phó Hiệu trưởng, Tổ trưởng chuyên môn và các bộ phận phụ trách</t>
+          <t>Rà soát, chuẩn bị đầy đủ phòng thi, camera giám sát, thiết bị PCCC, phòng bảo quản đề thi, bài thi phục vụ Điểm thi tốt nghiệp THPT năm 2026</t>
         </is>
       </c>
       <c r="C13" s="10" t="inlineStr">
         <is>
-          <t>N1_610 - Chủ trì xây dựng kế hoạch, chương trình công tác của Phòng</t>
+          <t>N1_580 - Phối hợp chuẩn bị các điều kiện về cơ sở vật chất, trang thiết bị phục vụ cho công tác tổ chức kỳ thi tuyển sinh 10; thi tốt ngh</t>
         </is>
       </c>
       <c r="D13" s="9" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>20/06/2026</t>
         </is>
       </c>
       <c r="E13" s="9" t="n">
@@ -781,27 +781,27 @@
       </c>
       <c r="H13" s="10" t="inlineStr">
         <is>
-          <t>Quyết định phân công nhiệm vụ cán bộ quản lý năm học</t>
+          <t>Biên bản kiểm tra điều kiện CSVC Điểm thi tốt nghiệp THPT năm 2026</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B14" s="10" t="inlineStr">
         <is>
-          <t>Tổ chức họp giao ban Ban Giám hiệu và họp Hội đồng sư phạm định kỳ hàng tháng</t>
+          <t>Phối hợp với chính quyền địa phương, công an, y tế bảo đảm an ninh trật tự, an toàn giao thông và phòng chống dịch bệnh kỳ thi tốt nghiệp</t>
         </is>
       </c>
       <c r="C14" s="10" t="inlineStr">
         <is>
-          <t>N1_611 - Tổ chức, điều hành, đánh giá kết quả thực hiện nhiệm vụ của công chức thuộc phòng</t>
+          <t>N1_580 - Phối hợp chuẩn bị các điều kiện về cơ sở vật chất, trang thiết bị phục vụ cho công tác tổ chức kỳ thi tuyển sinh 10; thi tốt ngh</t>
         </is>
       </c>
       <c r="D14" s="9" t="inlineStr">
         <is>
-          <t>31/05/2027</t>
+          <t>25/06/2026</t>
         </is>
       </c>
       <c r="E14" s="9" t="n">
@@ -815,27 +815,27 @@
       </c>
       <c r="H14" s="10" t="inlineStr">
         <is>
-          <t>Biên bản họp Hội đồng sư phạm từ tháng 9/2026 đến 5/2027</t>
+          <t>Kế hoạch phối hợp liên ngành bảo đảm an ninh trật tự kỳ thi</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B15" s="10" t="inlineStr">
         <is>
-          <t>Chỉ đạo, đôn đốc và đánh giá xếp loại thi đua cán bộ, giáo viên, nhân viên hàng tháng</t>
+          <t>Thành lập Hội đồng tuyển sinh lớp 10 THPT năm học 2026 - 2027; ban hành Thông báo hướng dẫn tuyển sinh</t>
         </is>
       </c>
       <c r="C15" s="10" t="inlineStr">
         <is>
-          <t>N1_611 - Tổ chức, điều hành, đánh giá kết quả thực hiện nhiệm vụ của công chức thuộc phòng</t>
+          <t>N2_1097 - Hướng dẫn tuyển sinh lớp 10 trung học phổ thông năm học 2026 - 2027</t>
         </is>
       </c>
       <c r="D15" s="9" t="inlineStr">
         <is>
-          <t>31/05/2027</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="E15" s="9" t="n">
@@ -849,27 +849,27 @@
       </c>
       <c r="H15" s="10" t="inlineStr">
         <is>
-          <t>Bảng tổng hợp xếp loại thi đua tháng các tổ</t>
+          <t>Quyết định thành lập HĐTS và Thông báo số 12/TB-THPT tuyển sinh lớp 10</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B16" s="10" t="inlineStr">
         <is>
-          <t>Kiểm tra, đôn đốc tiến độ thực hiện chương trình giảng dạy và quy chế chuyên môn toàn trường</t>
+          <t>Chỉ đạo thu nhận hồ sơ, xét tuyển, hoàn thành duyệt danh sách trúng tuyển lớp 10 trình Sở GD&amp;ĐT phê duyệt</t>
         </is>
       </c>
       <c r="C16" s="10" t="inlineStr">
         <is>
-          <t>N1_611 - Tổ chức, điều hành, đánh giá kết quả thực hiện nhiệm vụ của công chức thuộc phòng</t>
+          <t>N2_1097 - Hướng dẫn tuyển sinh lớp 10 trung học phổ thông năm học 2026 - 2027</t>
         </is>
       </c>
       <c r="D16" s="9" t="inlineStr">
         <is>
-          <t>31/05/2027</t>
+          <t>25/07/2026</t>
         </is>
       </c>
       <c r="E16" s="9" t="n">
@@ -883,7 +883,7 @@
       </c>
       <c r="H16" s="10" t="inlineStr">
         <is>
-          <t>Hồ sơ theo dõi tiến độ chương trình trên hệ thống VnEdu</t>
+          <t>Danh sách học sinh trúng tuyển lớp 10 đã được Sở GD&amp;ĐT phê duyệt</t>
         </is>
       </c>
     </row>
@@ -893,17 +893,17 @@
       </c>
       <c r="B17" s="10" t="inlineStr">
         <is>
-          <t>Ban hành Bộ tiêu chí và quy định đánh giá, xếp loại viên chức, người lao động năm học 2026 - 2027</t>
+          <t>Xây dựng Kế hoạch bồi dưỡng chính trị hè năm 2026 và bồi dưỡng chuyên môn nghiệp vụ cho cán bộ quản lý, giáo viên</t>
         </is>
       </c>
       <c r="C17" s="10" t="inlineStr">
         <is>
-          <t>N2_1046 - Tham mưu công tác đánh giá, xếp loại</t>
+          <t>N3_652 - Xây dựng Kế hoạch đào tạo, bồi dưỡng công chức, viên chức</t>
         </is>
       </c>
       <c r="D17" s="9" t="inlineStr">
         <is>
-          <t>15/10/2026</t>
+          <t>10/07/2026</t>
         </is>
       </c>
       <c r="E17" s="9" t="n">
@@ -917,27 +917,27 @@
       </c>
       <c r="H17" s="10" t="inlineStr">
         <is>
-          <t>Quy định số 02/QĐ-THPT về tiêu chí thi đua xếp loại</t>
+          <t>Kế hoạch số 45/KH-THPT bồi dưỡng chính trị và chuyên môn hè 2026</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B18" s="10" t="inlineStr">
         <is>
-          <t>Thành lập Hội đồng đánh giá, phân loại chất lượng viên chức và người lao động nhà trường</t>
+          <t>Chỉ đạo rà soát, xét duyệt quyết toán thu chi ngân sách 6 tháng đầu năm 2026 và đối chiếu kho bạc</t>
         </is>
       </c>
       <c r="C18" s="10" t="inlineStr">
         <is>
-          <t>N2_1046 - Tham mưu công tác đánh giá, xếp loại</t>
+          <t>N2_1158 - Xét duyệt quyết toán ngân sách Nhà nước hàng năm</t>
         </is>
       </c>
       <c r="D18" s="9" t="inlineStr">
         <is>
-          <t>15/05/2027</t>
+          <t>15/07/2026</t>
         </is>
       </c>
       <c r="E18" s="9" t="n">
@@ -951,27 +951,27 @@
       </c>
       <c r="H18" s="10" t="inlineStr">
         <is>
-          <t>Quyết định thành lập Hội đồng ĐGXL viên chức</t>
+          <t>Báo cáo quyết toán tài chính ngân sách 6 tháng đầu năm 2026</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B19" s="10" t="inlineStr">
         <is>
-          <t>Tổ chức đánh giá, tổng hợp kết quả và ban hành quyết định công nhận xếp loại viên chức cuối năm</t>
+          <t>Cử cán bộ quản lý, giáo viên tham gia đầy đủ các lớp tập huấn SGK, phương pháp giảng dạy và ứng dụng AI do Sở GD&amp;ĐT tổ chức</t>
         </is>
       </c>
       <c r="C19" s="10" t="inlineStr">
         <is>
-          <t>N2_1046 - Tham mưu công tác đánh giá, xếp loại</t>
+          <t>N3_652 - Xây dựng Kế hoạch đào tạo, bồi dưỡng công chức, viên chức</t>
         </is>
       </c>
       <c r="D19" s="9" t="inlineStr">
         <is>
-          <t>31/05/2027</t>
+          <t>15/08/2026</t>
         </is>
       </c>
       <c r="E19" s="9" t="n">
@@ -985,7 +985,7 @@
       </c>
       <c r="H19" s="10" t="inlineStr">
         <is>
-          <t>Biên bản họp xét thi đua và Thông báo kết quả ĐGXL</t>
+          <t>Quyết định cử cán bộ, giáo viên dự tập huấn hè năm 2026</t>
         </is>
       </c>
     </row>
@@ -995,17 +995,17 @@
       </c>
       <c r="B20" s="10" t="inlineStr">
         <is>
-          <t>Xây dựng và triển khai Kế hoạch kiểm tra nội bộ trường học năm học 2026 - 2027 (toàn diện &amp; chuyên đề)</t>
+          <t>Kiểm tra, nghiệm thu công tác sửa chữa phòng học, bàn ghế, hệ thống điện nước, mái che và vệ sinh khuôn viên trường trong hè</t>
         </is>
       </c>
       <c r="C20" s="10" t="inlineStr">
         <is>
-          <t>N2_1042 - Tham mưu công tác kiểm tra các kỳ thi, kiểm tra chuyên môn</t>
+          <t>N3_684 - Tham mưu triển khai công tác thuộc lĩnh vực Cơ sở vật chất</t>
         </is>
       </c>
       <c r="D20" s="9" t="inlineStr">
         <is>
-          <t>30/09/2026</t>
+          <t>15/08/2026</t>
         </is>
       </c>
       <c r="E20" s="9" t="n">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="H20" s="10" t="inlineStr">
         <is>
-          <t>Kế hoạch số 03/KH-KTNB và các biên bản kiểm tra chuyên đề</t>
+          <t>Biên bản nghiệm thu tu sửa cơ sở vật chất hè 2026</t>
         </is>
       </c>
     </row>
@@ -1029,17 +1029,17 @@
       </c>
       <c r="B21" s="10" t="inlineStr">
         <is>
-          <t>Kiểm tra hồ sơ chuyên môn, giáo án điện tử, sổ điểm và nền nếp dạy học của giáo viên</t>
+          <t>Rà soát, mua sắm bổ sung thiết bị dạy học tối thiểu, sách thư viện và hóa chất thí nghiệm chuẩn bị năm học mới 2026 - 2027</t>
         </is>
       </c>
       <c r="C21" s="10" t="inlineStr">
         <is>
-          <t>N2_1042 - Tham mưu công tác kiểm tra các kỳ thi, kiểm tra chuyên môn</t>
+          <t>N3_684 - Tham mưu triển khai công tác thuộc lĩnh vực Cơ sở vật chất</t>
         </is>
       </c>
       <c r="D21" s="9" t="inlineStr">
         <is>
-          <t>31/05/2027</t>
+          <t>25/08/2026</t>
         </is>
       </c>
       <c r="E21" s="9" t="n">
@@ -1053,27 +1053,27 @@
       </c>
       <c r="H21" s="10" t="inlineStr">
         <is>
-          <t>Biên bản kiểm tra hồ sơ giáo viên định kỳ 2 lần/học kỳ</t>
+          <t>Hợp đồng mua sắm thiết bị dạy học và sách thư viện</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B22" s="10" t="inlineStr">
         <is>
-          <t>Chỉ đạo và giám sát công tác tổ chức kiểm tra định kỳ (giữa kỳ, cuối kỳ) và thi thử tốt nghiệp THPT</t>
+          <t>Ban hành Quyết định phân công nhiệm vụ cán bộ quản lý, phân công chuyên môn giáo viên và biên chế học sinh các lớp năm học 2026 - 2027</t>
         </is>
       </c>
       <c r="C22" s="10" t="inlineStr">
         <is>
-          <t>N2_1042 - Tham mưu công tác kiểm tra các kỳ thi, kiểm tra chuyên môn</t>
+          <t>N1_585 - Chỉ đạo việc thực hiện các nhiệm vụ đầu năm học 2026 - 2027</t>
         </is>
       </c>
       <c r="D22" s="9" t="inlineStr">
         <is>
-          <t>31/05/2027</t>
+          <t>20/08/2026</t>
         </is>
       </c>
       <c r="E22" s="9" t="n">
@@ -1087,27 +1087,27 @@
       </c>
       <c r="H22" s="10" t="inlineStr">
         <is>
-          <t>Kế hoạch kiểm tra định kỳ và biên bản giám sát coi, chấm thi</t>
+          <t>Quyết định số 102/QĐ-THPT về phân công nhiệm vụ năm học 2026-2027</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B23" s="10" t="inlineStr">
         <is>
-          <t>Xây dựng Kế hoạch ôn tập tốt nghiệp THPT năm 2027 cho học sinh khối 12; phân công GV cốt cán phụ trách</t>
+          <t>Chỉ đạo tổ chức ngày tựu trường, đón học sinh lớp 10 và tổ chức tuần sinh hoạt tập thể đầu năm học 2026 - 2027</t>
         </is>
       </c>
       <c r="C23" s="10" t="inlineStr">
         <is>
-          <t>N3_661 - Ban hành Kế hoạch tổ chức kỳ thi tốt nghiệp THPT năm 2026 của Sở GDĐT</t>
+          <t>N1_585 - Chỉ đạo việc thực hiện các nhiệm vụ đầu năm học 2026 - 2027</t>
         </is>
       </c>
       <c r="D23" s="9" t="inlineStr">
         <is>
-          <t>15/11/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
       <c r="E23" s="9" t="n">
@@ -1121,27 +1121,27 @@
       </c>
       <c r="H23" s="10" t="inlineStr">
         <is>
-          <t>Kế hoạch ôn tập tốt nghiệp THPT năm học 2026-2027</t>
+          <t>Kế hoạch tựu trường và tuần sinh hoạt tập thể học sinh đầu năm</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B24" s="10" t="inlineStr">
         <is>
-          <t>Tổ chức các đợt thi thử tốt nghiệp THPT, phân tích phổ điểm để chỉ đạo đổi mới phương pháp dạy ôn</t>
+          <t>Xây dựng Kế hoạch và chỉ đạo tổ chức Lễ Khai giảng năm học mới 2026 - 2027 trang trọng, ý nghĩa, an toàn và tiết kiệm</t>
         </is>
       </c>
       <c r="C24" s="10" t="inlineStr">
         <is>
-          <t>N3_661 - Ban hành Kế hoạch tổ chức kỳ thi tốt nghiệp THPT năm 2026 của Sở GDĐT</t>
+          <t>N3_666 - Kế hoạch tham dự Lễ Khai giảng năm học 2026 - 2027 tại các cơ sở giáo dục trên địa bàn tỉnh Cao Bằng</t>
         </is>
       </c>
       <c r="D24" s="9" t="inlineStr">
         <is>
-          <t>20/05/2027</t>
+          <t>05/09/2026</t>
         </is>
       </c>
       <c r="E24" s="9" t="n">
@@ -1155,27 +1155,27 @@
       </c>
       <c r="H24" s="10" t="inlineStr">
         <is>
-          <t>Báo cáo phân tích phổ điểm các đợt thi khảo sát khối 12</t>
+          <t>Kế hoạch tổ chức Lễ Khai giảng năm học 2026-2027</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B25" s="10" t="inlineStr">
         <is>
-          <t>Chuẩn bị đầy đủ các điều kiện cơ sở vật chất, an ninh trật tự phục vụ Điểm thi tốt nghiệp THPT</t>
+          <t>Xây dựng và ban hành Kế hoạch giáo dục nhà trường, kế hoạch thực hiện nhiệm vụ trọng tâm năm học 2026 - 2027</t>
         </is>
       </c>
       <c r="C25" s="10" t="inlineStr">
         <is>
-          <t>N3_661 - Ban hành Kế hoạch tổ chức kỳ thi tốt nghiệp THPT năm 2026 của Sở GDĐT</t>
+          <t>N3_668 - Quyết định ban hành Kế hoạch nhiệm vụ, giải pháp trọng tâm năm học 2026 - 2027 của ngành Giáo dục tỉnh Cao Bằng</t>
         </is>
       </c>
       <c r="D25" s="9" t="inlineStr">
         <is>
-          <t>20/06/2027</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="E25" s="9" t="n">
@@ -1189,27 +1189,27 @@
       </c>
       <c r="H25" s="10" t="inlineStr">
         <is>
-          <t>Biên bản kiểm tra cơ sở vật chất Điểm thi tốt nghiệp</t>
+          <t>Kế hoạch giáo dục nhà trường năm học 2026-2027</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B26" s="10" t="inlineStr">
         <is>
-          <t>Chỉ đạo xây dựng dự toán ngân sách Nhà nước và Quy chế chi tiêu nội bộ năm học 2026 - 2027</t>
+          <t>Phê duyệt kế hoạch giáo dục của các tổ chuyên môn, tổ văn phòng và các bộ phận trong nhà trường năm học 2026 - 2027</t>
         </is>
       </c>
       <c r="C26" s="10" t="inlineStr">
         <is>
-          <t>N2_1150 - Xây dựng dự toán ngân sách Nhà nước hàng năm</t>
+          <t>N3_668 - Quyết định ban hành Kế hoạch nhiệm vụ, giải pháp trọng tâm năm học 2026 - 2027 của ngành Giáo dục tỉnh Cao Bằng</t>
         </is>
       </c>
       <c r="D26" s="9" t="inlineStr">
         <is>
-          <t>31/10/2026</t>
+          <t>18/09/2026</t>
         </is>
       </c>
       <c r="E26" s="9" t="n">
@@ -1223,27 +1223,27 @@
       </c>
       <c r="H26" s="10" t="inlineStr">
         <is>
-          <t>Dự toán ngân sách năm 2027 và Quy chế chi tiêu nội bộ sửa đổi</t>
+          <t>Kế hoạch năm học các tổ TN, XH, VP đã phê duyệt</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B27" s="10" t="inlineStr">
         <is>
-          <t>Quản lý, sử dụng nguồn tài chính ngân sách đúng quy định, công khai minh bạch tài chính trường học</t>
+          <t>Chỉ đạo tổ chức thành công Hội nghị cán bộ, viên chức, người lao động năm học 2026 - 2027</t>
         </is>
       </c>
       <c r="C27" s="10" t="inlineStr">
         <is>
-          <t>N2_1150 - Xây dựng dự toán ngân sách Nhà nước hàng năm</t>
+          <t>N3_668 - Quyết định ban hành Kế hoạch nhiệm vụ, giải pháp trọng tâm năm học 2026 - 2027 của ngành Giáo dục tỉnh Cao Bằng</t>
         </is>
       </c>
       <c r="D27" s="9" t="inlineStr">
         <is>
-          <t>31/05/2027</t>
+          <t>28/09/2026</t>
         </is>
       </c>
       <c r="E27" s="9" t="n">
@@ -1257,7 +1257,7 @@
       </c>
       <c r="H27" s="10" t="inlineStr">
         <is>
-          <t>Báo cáo công khai tài chính định kỳ quý, năm theo Thông tư</t>
+          <t>Nghị quyết Hội nghị CBVC-NLĐ năm học 2026-2027</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B28" s="10" t="inlineStr">
         <is>
-          <t>Rà soát, mua sắm bổ sung, sửa chữa cơ sở vật chất, thiết bị dạy học phục vụ năm học mới 2026 - 2027</t>
+          <t>Xây dựng lịch công tác tuần, tháng 9 và chương trình điều hành tổng thể hoạt động sư phạm toàn trường</t>
         </is>
       </c>
       <c r="C28" s="10" t="inlineStr">
         <is>
-          <t>N3_684 - Tham mưu triển khai công tác thuộc lĩnh vực Cơ sở vật chất</t>
+          <t>N1_610 - Chủ trì xây dựng kế hoạch, chương trình công tác của Phòng</t>
         </is>
       </c>
       <c r="D28" s="9" t="inlineStr">
@@ -1291,27 +1291,27 @@
       </c>
       <c r="H28" s="10" t="inlineStr">
         <is>
-          <t>Biên bản kiểm kê và danh mục mua sắm sửa chữa tài sản</t>
+          <t>Lịch công tác tuần tháng 9/2026 đăng tải trên cổng thông tin điện tử</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B29" s="10" t="inlineStr">
         <is>
-          <t>Chỉ đạo công tác bảo đảm an toàn trường học, phòng chống cháy nổ, vệ sinh môi trường xanh - sạch - đẹp</t>
+          <t>Tổ chức họp giao ban BGH và họp Hội đồng sư phạm tháng 9/2026 đánh giá triển khai nhiệm vụ năm học mới</t>
         </is>
       </c>
       <c r="C29" s="10" t="inlineStr">
         <is>
-          <t>N3_684 - Tham mưu triển khai công tác thuộc lĩnh vực Cơ sở vật chất</t>
+          <t>N1_611 - Tổ chức, điều hành, đánh giá kết quả thực hiện nhiệm vụ của công chức thuộc phòng</t>
         </is>
       </c>
       <c r="D29" s="9" t="inlineStr">
         <is>
-          <t>31/05/2027</t>
+          <t>15/09/2026</t>
         </is>
       </c>
       <c r="E29" s="9" t="n">
@@ -1325,27 +1325,27 @@
       </c>
       <c r="H29" s="10" t="inlineStr">
         <is>
-          <t>Kế hoạch an toàn trường học và biên bản tự kiểm tra PCCC</t>
+          <t>Biên bản họp Hội đồng sư phạm tháng 9/2026</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B30" s="10" t="inlineStr">
         <is>
-          <t>Ban hành Thông báo Lịch tiếp công dân của Hiệu trưởng, bố trí phòng tiếp dân và mở sổ theo dõi tiếp dân</t>
+          <t>Kiểm tra, đôn đốc tiến độ thực hiện chương trình giảng dạy và nền nếp chuyên môn tháng 9</t>
         </is>
       </c>
       <c r="C30" s="10" t="inlineStr">
         <is>
-          <t>N1_572 - Tiếp công dân định kỳ cùng Giám đốc Sở GDĐT</t>
+          <t>N1_611 - Tổ chức, điều hành, đánh giá kết quả thực hiện nhiệm vụ của công chức thuộc phòng</t>
         </is>
       </c>
       <c r="D30" s="9" t="inlineStr">
         <is>
-          <t>15/09/2026</t>
+          <t>30/09/2026</t>
         </is>
       </c>
       <c r="E30" s="9" t="n">
@@ -1359,27 +1359,27 @@
       </c>
       <c r="H30" s="10" t="inlineStr">
         <is>
-          <t>Thông báo lịch tiếp công dân năm học 2026-2027</t>
+          <t>Báo cáo kiểm tra nền nếp dạy học tháng 9/2026</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B31" s="10" t="inlineStr">
         <is>
-          <t>Thực hiện tiếp công dân định kỳ và đột xuất; xử lý, giải quyết kịp thời đơn thư khiếu nại, phản ánh</t>
+          <t>Tổng hợp số liệu đầu năm, kiểm tra việc ổn định nền nếp dạy học tháng 9 và báo cáo Sở GD&amp;ĐT đúng thời hạn</t>
         </is>
       </c>
       <c r="C31" s="10" t="inlineStr">
         <is>
-          <t>N1_572 - Tiếp công dân định kỳ cùng Giám đốc Sở GDĐT</t>
+          <t>N2_1131 - Tổng hợp báo cáo tình hình triển khai nhiệm vụ đầu năm học 2026 - 2027</t>
         </is>
       </c>
       <c r="D31" s="9" t="inlineStr">
         <is>
-          <t>31/05/2027</t>
+          <t>20/09/2026</t>
         </is>
       </c>
       <c r="E31" s="9" t="n">
@@ -1393,27 +1393,27 @@
       </c>
       <c r="H31" s="10" t="inlineStr">
         <is>
-          <t>Sổ theo dõi tiếp công dân và giải quyết khiếu nại kiến nghị</t>
+          <t>Báo cáo tình hình triển khai nhiệm vụ đầu năm học gửi Sở GD&amp;ĐT</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B32" s="10" t="inlineStr">
         <is>
-          <t>Chỉ đạo triển khai mạnh mẽ ứng dụng CNTT, phần mềm quản lý trường học VnEdu, học bạ số và chữ ký số</t>
+          <t>Chỉ đạo triển khai công tác tuyên truyền phổ biến pháp luật, an toàn giao thông và cam kết an ninh trật tự trường học tháng 9</t>
         </is>
       </c>
       <c r="C32" s="10" t="inlineStr">
         <is>
-          <t>N2_1107 - Báo cáo tổng kết đánh giá tình hình triển khai nhiệm vụ ứng dụng công nghệ thông tin và chuyển đổi số</t>
+          <t>N2_1131 - Tổng hợp báo cáo tình hình triển khai nhiệm vụ đầu năm học 2026 - 2027</t>
         </is>
       </c>
       <c r="D32" s="9" t="inlineStr">
         <is>
-          <t>31/05/2027</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="E32" s="9" t="n">
@@ -1427,27 +1427,27 @@
       </c>
       <c r="H32" s="10" t="inlineStr">
         <is>
-          <t>Hồ sơ triển khai 100% học bạ số và chữ ký số giáo viên</t>
+          <t>Bản cam kết an toàn giao thông và phòng chống bạo lực học đường</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B33" s="10" t="inlineStr">
         <is>
-          <t>Xây dựng báo cáo tổng kết chuyển đổi số và phát triển kho học liệu điện tử phục vụ giáo viên, học sinh</t>
+          <t>Ban hành Thông báo Lịch tiếp công dân năm học 2026 - 2027; tiếp nhận và giải quyết kịp thời phản ánh của phụ huynh đầu năm học</t>
         </is>
       </c>
       <c r="C33" s="10" t="inlineStr">
         <is>
-          <t>N2_1107 - Báo cáo tổng kết đánh giá tình hình triển khai nhiệm vụ ứng dụng công nghệ thông tin và chuyển đổi số</t>
+          <t>N1_572 - Tiếp công dân định kỳ cùng Giám đốc Sở GDĐT</t>
         </is>
       </c>
       <c r="D33" s="9" t="inlineStr">
         <is>
-          <t>31/05/2027</t>
+          <t>15/09/2026</t>
         </is>
       </c>
       <c r="E33" s="9" t="n">
@@ -1461,7 +1461,7 @@
       </c>
       <c r="H33" s="10" t="inlineStr">
         <is>
-          <t>Báo cáo chuyển đổi số ngành giáo dục năm học 2026-2027</t>
+          <t>Thông báo lịch tiếp công dân năm học 2026-2027 và sổ tiếp dân</t>
         </is>
       </c>
     </row>

--- a/public/downloads/Import_cong_viec_CBQL.xlsx
+++ b/public/downloads/Import_cong_viec_CBQL.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Mẫu import" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="SPCV" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mẫu import" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SPCV" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -520,7 +520,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:L75"/>
+  <dimension ref="A2:L199"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -621,17 +621,17 @@
       </c>
       <c r="B9" s="10" t="inlineStr">
         <is>
-          <t>Tổng hợp kết quả đánh giá, xếp loại chất lượng viên chức, người lao động cuối năm học 2025 - 2026 theo Nghị định 90/2020 &amp; 48/2023</t>
+          <t>Chỉ đạo hoàn thành chương trình dạy học học kỳ II, tổ chức ôn tập và kiểm tra đánh giá cuối học kỳ II năm học 2025 - 2026</t>
         </is>
       </c>
       <c r="C9" s="10" t="inlineStr">
         <is>
-          <t>N2_1046 - Tham mưu công tác đánh giá, xếp loại</t>
+          <t>N2_1115 - Kế hoạch triển khai hoạt động chuyên môn</t>
         </is>
       </c>
       <c r="D9" s="9" t="inlineStr">
         <is>
-          <t>10/06/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="E9" s="9" t="n">
@@ -645,27 +645,27 @@
       </c>
       <c r="H9" s="10" t="inlineStr">
         <is>
-          <t>Biên bản họp Hội đồng đánh giá xếp loại viên chức năm học 2025-2026</t>
+          <t>Kế hoạch kiểm tra cuối học kỳ II năm học 2025-2026</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B10" s="10" t="inlineStr">
         <is>
-          <t>Ban hành Quyết định công nhận kết quả đánh giá, xếp loại viên chức, người lao động và công khai toàn trường</t>
+          <t>Chỉ đạo thu nhận, kiểm tra, rà soát hồ sơ và hoàn thành dữ liệu đăng ký dự thi tốt nghiệp THPT năm 2026 trên Cổng Quản lý thi</t>
         </is>
       </c>
       <c r="C10" s="10" t="inlineStr">
         <is>
-          <t>N2_1046 - Tham mưu công tác đánh giá, xếp loại</t>
+          <t>N2_1102 - Tổ chức đăng ký dự thi và nhận dữ liệu đăng ký dự thi tốt nghiệp THPT; đăng ký dự thi đăng ký xét tuyển sinh đại học, cao đẳng g</t>
         </is>
       </c>
       <c r="D10" s="9" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="E10" s="9" t="n">
@@ -679,7 +679,7 @@
       </c>
       <c r="H10" s="10" t="inlineStr">
         <is>
-          <t>Quyết định số 85/QĐ-THPT công nhận kết quả xếp loại</t>
+          <t>Danh sách thí sinh đăng ký dự thi tốt nghiệp THPT 2026 đã duyệt</t>
         </is>
       </c>
     </row>
@@ -689,17 +689,17 @@
       </c>
       <c r="B11" s="10" t="inlineStr">
         <is>
-          <t>Chỉ đạo thẩm định hồ sơ thi đua, sáng kiến kinh nghiệm của CBGVNV đề nghị công nhận LĐTT, CSTĐ cơ sở năm học 2025 - 2026</t>
+          <t>Chỉ đạo rà soát, kiểm tra học bạ số và đồng bộ dữ liệu điểm học tập cấp THPT lên Hệ thống Quản lý thi của Bộ GD&amp;ĐT</t>
         </is>
       </c>
       <c r="C11" s="10" t="inlineStr">
         <is>
-          <t>N1_576 - Tiếp nhận, thẩm định hồ sơ đề nghị xét tặng thưởng danh hiệu Lao động tiên tiến, Chiến sỹ thi đua cơ sở và hồ sơ trình khen thưở</t>
+          <t>N2_1095 - Chỉ đạo, tổ chức rà soát kết quả điểm học tập cấp THPT (học bạ) trên Hệ thống Quản lý thi theo Chỉ đạo của Bộ GDĐT</t>
         </is>
       </c>
       <c r="D11" s="9" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="E11" s="9" t="n">
@@ -713,27 +713,27 @@
       </c>
       <c r="H11" s="10" t="inlineStr">
         <is>
-          <t>Biên bản thẩm định hồ sơ sáng kiến kinh nghiệm và thi đua</t>
+          <t>Biên bản rà soát học bạ điện tử khối 12 trên hệ thống thi</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B12" s="10" t="inlineStr">
         <is>
-          <t>Tổ chức họp Hội đồng Thi đua - Khen thưởng nhà trường xét duyệt danh hiệu và hoàn thiện tờ trình nộp Sở GD&amp;ĐT</t>
+          <t>Tổ chức kỳ thi thử tốt nghiệp THPT năm 2026 đợt cuối cho học sinh lớp 12, phân tích phổ điểm để điều chỉnh phương pháp ôn tập</t>
         </is>
       </c>
       <c r="C12" s="10" t="inlineStr">
         <is>
-          <t>N1_576 - Tiếp nhận, thẩm định hồ sơ đề nghị xét tặng thưởng danh hiệu Lao động tiên tiến, Chiến sỹ thi đua cơ sở và hồ sơ trình khen thưở</t>
+          <t>N2_1091 - Tổ chức thi thử tốt nghiệp THPT năm 2026 (ra đề, in sao đề thi)</t>
         </is>
       </c>
       <c r="D12" s="9" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="E12" s="9" t="n">
@@ -747,7 +747,7 @@
       </c>
       <c r="H12" s="10" t="inlineStr">
         <is>
-          <t>Tờ trình số 28/TTr-THPT đề nghị khen thưởng năm học 2025-2026</t>
+          <t>Báo cáo phân tích phổ điểm thi thử tốt nghiệp THPT 2026</t>
         </is>
       </c>
     </row>
@@ -757,17 +757,17 @@
       </c>
       <c r="B13" s="10" t="inlineStr">
         <is>
-          <t>Rà soát, chuẩn bị đầy đủ phòng thi, camera giám sát, thiết bị PCCC, phòng bảo quản đề thi, bài thi phục vụ Điểm thi tốt nghiệp THPT năm 2026</t>
+          <t>Chỉ đạo tổng kết đánh giá xếp loại học sinh, tổng kết công tác chuyên môn và lập báo cáo thống kê cuối năm học 2025 - 2026 nộp Sở GD&amp;ĐT</t>
         </is>
       </c>
       <c r="C13" s="10" t="inlineStr">
         <is>
-          <t>N1_580 - Phối hợp chuẩn bị các điều kiện về cơ sở vật chất, trang thiết bị phục vụ cho công tác tổ chức kỳ thi tuyển sinh 10; thi tốt ngh</t>
+          <t>N2_1126 - Tổng hợp báo cáo thống kê kỳ cuối năm học 2025 - 2026</t>
         </is>
       </c>
       <c r="D13" s="9" t="inlineStr">
         <is>
-          <t>20/06/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="E13" s="9" t="n">
@@ -781,27 +781,27 @@
       </c>
       <c r="H13" s="10" t="inlineStr">
         <is>
-          <t>Biên bản kiểm tra điều kiện CSVC Điểm thi tốt nghiệp THPT năm 2026</t>
+          <t>Báo cáo tổng kết năm học 2025-2026 trường THPT Phục Hòa</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B14" s="10" t="inlineStr">
         <is>
-          <t>Phối hợp với chính quyền địa phương, công an, y tế bảo đảm an ninh trật tự, an toàn giao thông và phòng chống dịch bệnh kỳ thi tốt nghiệp</t>
+          <t>Xây dựng Kế hoạch và chỉ đạo tổ chức Lễ Bế giảng năm học 2025 - 2026, Lễ Tri ân và Trưởng thành cho học sinh niên khóa 2023 - 2026</t>
         </is>
       </c>
       <c r="C14" s="10" t="inlineStr">
         <is>
-          <t>N1_580 - Phối hợp chuẩn bị các điều kiện về cơ sở vật chất, trang thiết bị phục vụ cho công tác tổ chức kỳ thi tuyển sinh 10; thi tốt ngh</t>
+          <t>N1_610 - Chủ trì xây dựng kế hoạch, chương trình công tác của Phòng</t>
         </is>
       </c>
       <c r="D14" s="9" t="inlineStr">
         <is>
-          <t>25/06/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="E14" s="9" t="n">
@@ -815,7 +815,7 @@
       </c>
       <c r="H14" s="10" t="inlineStr">
         <is>
-          <t>Kế hoạch phối hợp liên ngành bảo đảm an ninh trật tự kỳ thi</t>
+          <t>Kế hoạch tổ chức Lễ Bế giảng và Tri ân trưởng thành năm học 2025-2026</t>
         </is>
       </c>
     </row>
@@ -825,17 +825,17 @@
       </c>
       <c r="B15" s="10" t="inlineStr">
         <is>
-          <t>Thành lập Hội đồng tuyển sinh lớp 10 THPT năm học 2026 - 2027; ban hành Thông báo hướng dẫn tuyển sinh</t>
+          <t>Tổ chức họp giao ban BGH và họp Hội đồng sư phạm tháng 5/2026 rà soát nhiệm vụ kết thúc năm học và triển khai hoạt động hè</t>
         </is>
       </c>
       <c r="C15" s="10" t="inlineStr">
         <is>
-          <t>N2_1097 - Hướng dẫn tuyển sinh lớp 10 trung học phổ thông năm học 2026 - 2027</t>
+          <t>N1_611 - Tổ chức, điều hành, đánh giá kết quả thực hiện nhiệm vụ của công chức thuộc phòng</t>
         </is>
       </c>
       <c r="D15" s="9" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="E15" s="9" t="n">
@@ -849,27 +849,27 @@
       </c>
       <c r="H15" s="10" t="inlineStr">
         <is>
-          <t>Quyết định thành lập HĐTS và Thông báo số 12/TB-THPT tuyển sinh lớp 10</t>
+          <t>Biên bản họp Hội đồng sư phạm tháng 5/2026</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B16" s="10" t="inlineStr">
         <is>
-          <t>Chỉ đạo thu nhận hồ sơ, xét tuyển, hoàn thành duyệt danh sách trúng tuyển lớp 10 trình Sở GD&amp;ĐT phê duyệt</t>
+          <t>Duy trì lịch tiếp công dân định kỳ tháng 5/2026, lắng nghe và giải quyết kịp thời thắc mắc của phụ huynh học sinh cuối năm học</t>
         </is>
       </c>
       <c r="C16" s="10" t="inlineStr">
         <is>
-          <t>N2_1097 - Hướng dẫn tuyển sinh lớp 10 trung học phổ thông năm học 2026 - 2027</t>
+          <t>N1_572 - Tiếp công dân định kỳ cùng Giám đốc Sở GDĐT</t>
         </is>
       </c>
       <c r="D16" s="9" t="inlineStr">
         <is>
-          <t>25/07/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="E16" s="9" t="n">
@@ -883,7 +883,7 @@
       </c>
       <c r="H16" s="10" t="inlineStr">
         <is>
-          <t>Danh sách học sinh trúng tuyển lớp 10 đã được Sở GD&amp;ĐT phê duyệt</t>
+          <t>Sổ theo dõi tiếp công dân tháng 5/2026</t>
         </is>
       </c>
     </row>
@@ -893,17 +893,17 @@
       </c>
       <c r="B17" s="10" t="inlineStr">
         <is>
-          <t>Xây dựng Kế hoạch bồi dưỡng chính trị hè năm 2026 và bồi dưỡng chuyên môn nghiệp vụ cho cán bộ quản lý, giáo viên</t>
+          <t>Tổng hợp kết quả đánh giá, xếp loại chất lượng viên chức, người lao động cuối năm học 2025 - 2026 theo Nghị định 90/2020 &amp; 48/2023</t>
         </is>
       </c>
       <c r="C17" s="10" t="inlineStr">
         <is>
-          <t>N3_652 - Xây dựng Kế hoạch đào tạo, bồi dưỡng công chức, viên chức</t>
+          <t>N2_1046 - Tham mưu công tác đánh giá, xếp loại</t>
         </is>
       </c>
       <c r="D17" s="9" t="inlineStr">
         <is>
-          <t>10/07/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
       <c r="E17" s="9" t="n">
@@ -917,27 +917,27 @@
       </c>
       <c r="H17" s="10" t="inlineStr">
         <is>
-          <t>Kế hoạch số 45/KH-THPT bồi dưỡng chính trị và chuyên môn hè 2026</t>
+          <t>Biên bản họp Hội đồng đánh giá xếp loại viên chức năm học 2025-2026</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B18" s="10" t="inlineStr">
         <is>
-          <t>Chỉ đạo rà soát, xét duyệt quyết toán thu chi ngân sách 6 tháng đầu năm 2026 và đối chiếu kho bạc</t>
+          <t>Ban hành Quyết định công nhận kết quả đánh giá, xếp loại viên chức, người lao động và công khai toàn trường</t>
         </is>
       </c>
       <c r="C18" s="10" t="inlineStr">
         <is>
-          <t>N2_1158 - Xét duyệt quyết toán ngân sách Nhà nước hàng năm</t>
+          <t>N2_1046 - Tham mưu công tác đánh giá, xếp loại</t>
         </is>
       </c>
       <c r="D18" s="9" t="inlineStr">
         <is>
-          <t>15/07/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="E18" s="9" t="n">
@@ -951,27 +951,27 @@
       </c>
       <c r="H18" s="10" t="inlineStr">
         <is>
-          <t>Báo cáo quyết toán tài chính ngân sách 6 tháng đầu năm 2026</t>
+          <t>Quyết định số 85/QĐ-THPT công nhận kết quả xếp loại</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B19" s="10" t="inlineStr">
         <is>
-          <t>Cử cán bộ quản lý, giáo viên tham gia đầy đủ các lớp tập huấn SGK, phương pháp giảng dạy và ứng dụng AI do Sở GD&amp;ĐT tổ chức</t>
+          <t>Chỉ đạo thẩm định hồ sơ thi đua, sáng kiến kinh nghiệm của CBGVNV đề nghị công nhận LĐTT, CSTĐ cơ sở năm học 2025 - 2026</t>
         </is>
       </c>
       <c r="C19" s="10" t="inlineStr">
         <is>
-          <t>N3_652 - Xây dựng Kế hoạch đào tạo, bồi dưỡng công chức, viên chức</t>
+          <t>N1_576 - Tiếp nhận, thẩm định hồ sơ đề nghị xét tặng thưởng danh hiệu Lao động tiên tiến, Chiến sỹ thi đua cơ sở và hồ sơ trình khen thưở</t>
         </is>
       </c>
       <c r="D19" s="9" t="inlineStr">
         <is>
-          <t>15/08/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="E19" s="9" t="n">
@@ -985,27 +985,27 @@
       </c>
       <c r="H19" s="10" t="inlineStr">
         <is>
-          <t>Quyết định cử cán bộ, giáo viên dự tập huấn hè năm 2026</t>
+          <t>Biên bản thẩm định hồ sơ sáng kiến kinh nghiệm và thi đua</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B20" s="10" t="inlineStr">
         <is>
-          <t>Kiểm tra, nghiệm thu công tác sửa chữa phòng học, bàn ghế, hệ thống điện nước, mái che và vệ sinh khuôn viên trường trong hè</t>
+          <t>Tổ chức họp Hội đồng Thi đua - Khen thưởng nhà trường xét duyệt danh hiệu và hoàn thiện tờ trình nộp Sở GD&amp;ĐT</t>
         </is>
       </c>
       <c r="C20" s="10" t="inlineStr">
         <is>
-          <t>N3_684 - Tham mưu triển khai công tác thuộc lĩnh vực Cơ sở vật chất</t>
+          <t>N1_576 - Tiếp nhận, thẩm định hồ sơ đề nghị xét tặng thưởng danh hiệu Lao động tiên tiến, Chiến sỹ thi đua cơ sở và hồ sơ trình khen thưở</t>
         </is>
       </c>
       <c r="D20" s="9" t="inlineStr">
         <is>
-          <t>15/08/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="E20" s="9" t="n">
@@ -1019,27 +1019,27 @@
       </c>
       <c r="H20" s="10" t="inlineStr">
         <is>
-          <t>Biên bản nghiệm thu tu sửa cơ sở vật chất hè 2026</t>
+          <t>Tờ trình số 28/TTr-THPT đề nghị khen thưởng năm học 2025-2026</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B21" s="10" t="inlineStr">
         <is>
-          <t>Rà soát, mua sắm bổ sung thiết bị dạy học tối thiểu, sách thư viện và hóa chất thí nghiệm chuẩn bị năm học mới 2026 - 2027</t>
+          <t>Rà soát, chuẩn bị đầy đủ phòng thi, camera giám sát, thiết bị PCCC, phòng bảo quản đề thi, bài thi phục vụ Điểm thi tốt nghiệp THPT năm 2026</t>
         </is>
       </c>
       <c r="C21" s="10" t="inlineStr">
         <is>
-          <t>N3_684 - Tham mưu triển khai công tác thuộc lĩnh vực Cơ sở vật chất</t>
+          <t>N1_580 - Phối hợp chuẩn bị các điều kiện về cơ sở vật chất, trang thiết bị phục vụ cho công tác tổ chức kỳ thi tuyển sinh 10; thi tốt ngh</t>
         </is>
       </c>
       <c r="D21" s="9" t="inlineStr">
         <is>
-          <t>25/08/2026</t>
+          <t>20/06/2026</t>
         </is>
       </c>
       <c r="E21" s="9" t="n">
@@ -1053,27 +1053,27 @@
       </c>
       <c r="H21" s="10" t="inlineStr">
         <is>
-          <t>Hợp đồng mua sắm thiết bị dạy học và sách thư viện</t>
+          <t>Biên bản kiểm tra điều kiện CSVC Điểm thi tốt nghiệp THPT năm 2026</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B22" s="10" t="inlineStr">
         <is>
-          <t>Ban hành Quyết định phân công nhiệm vụ cán bộ quản lý, phân công chuyên môn giáo viên và biên chế học sinh các lớp năm học 2026 - 2027</t>
+          <t>Phối hợp với chính quyền địa phương, công an, y tế bảo đảm an ninh trật tự, an toàn giao thông và phòng chống dịch bệnh kỳ thi tốt nghiệp</t>
         </is>
       </c>
       <c r="C22" s="10" t="inlineStr">
         <is>
-          <t>N1_585 - Chỉ đạo việc thực hiện các nhiệm vụ đầu năm học 2026 - 2027</t>
+          <t>N1_580 - Phối hợp chuẩn bị các điều kiện về cơ sở vật chất, trang thiết bị phục vụ cho công tác tổ chức kỳ thi tuyển sinh 10; thi tốt ngh</t>
         </is>
       </c>
       <c r="D22" s="9" t="inlineStr">
         <is>
-          <t>20/08/2026</t>
+          <t>25/06/2026</t>
         </is>
       </c>
       <c r="E22" s="9" t="n">
@@ -1087,27 +1087,27 @@
       </c>
       <c r="H22" s="10" t="inlineStr">
         <is>
-          <t>Quyết định số 102/QĐ-THPT về phân công nhiệm vụ năm học 2026-2027</t>
+          <t>Kế hoạch phối hợp liên ngành bảo đảm an ninh trật tự kỳ thi</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B23" s="10" t="inlineStr">
         <is>
-          <t>Chỉ đạo tổ chức ngày tựu trường, đón học sinh lớp 10 và tổ chức tuần sinh hoạt tập thể đầu năm học 2026 - 2027</t>
+          <t>Thành lập Hội đồng tuyển sinh lớp 10 THPT năm học 2026 - 2027; ban hành Thông báo hướng dẫn tuyển sinh</t>
         </is>
       </c>
       <c r="C23" s="10" t="inlineStr">
         <is>
-          <t>N1_585 - Chỉ đạo việc thực hiện các nhiệm vụ đầu năm học 2026 - 2027</t>
+          <t>N2_1097 - Hướng dẫn tuyển sinh lớp 10 trung học phổ thông năm học 2026 - 2027</t>
         </is>
       </c>
       <c r="D23" s="9" t="inlineStr">
         <is>
-          <t>28/08/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="E23" s="9" t="n">
@@ -1121,27 +1121,27 @@
       </c>
       <c r="H23" s="10" t="inlineStr">
         <is>
-          <t>Kế hoạch tựu trường và tuần sinh hoạt tập thể học sinh đầu năm</t>
+          <t>Quyết định thành lập HĐTS và Thông báo số 12/TB-THPT tuyển sinh lớp 10</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B24" s="10" t="inlineStr">
         <is>
-          <t>Xây dựng Kế hoạch và chỉ đạo tổ chức Lễ Khai giảng năm học mới 2026 - 2027 trang trọng, ý nghĩa, an toàn và tiết kiệm</t>
+          <t>Chỉ đạo thu nhận hồ sơ, xét tuyển, hoàn thành duyệt danh sách trúng tuyển lớp 10 trình Sở GD&amp;ĐT phê duyệt</t>
         </is>
       </c>
       <c r="C24" s="10" t="inlineStr">
         <is>
-          <t>N3_666 - Kế hoạch tham dự Lễ Khai giảng năm học 2026 - 2027 tại các cơ sở giáo dục trên địa bàn tỉnh Cao Bằng</t>
+          <t>N2_1097 - Hướng dẫn tuyển sinh lớp 10 trung học phổ thông năm học 2026 - 2027</t>
         </is>
       </c>
       <c r="D24" s="9" t="inlineStr">
         <is>
-          <t>05/09/2026</t>
+          <t>25/07/2026</t>
         </is>
       </c>
       <c r="E24" s="9" t="n">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="H24" s="10" t="inlineStr">
         <is>
-          <t>Kế hoạch tổ chức Lễ Khai giảng năm học 2026-2027</t>
+          <t>Danh sách học sinh trúng tuyển lớp 10 đã được Sở GD&amp;ĐT phê duyệt</t>
         </is>
       </c>
     </row>
@@ -1165,17 +1165,17 @@
       </c>
       <c r="B25" s="10" t="inlineStr">
         <is>
-          <t>Xây dựng và ban hành Kế hoạch giáo dục nhà trường, kế hoạch thực hiện nhiệm vụ trọng tâm năm học 2026 - 2027</t>
+          <t>Xây dựng Kế hoạch bồi dưỡng chính trị hè năm 2026 và bồi dưỡng chuyên môn nghiệp vụ cho cán bộ quản lý, giáo viên</t>
         </is>
       </c>
       <c r="C25" s="10" t="inlineStr">
         <is>
-          <t>N3_668 - Quyết định ban hành Kế hoạch nhiệm vụ, giải pháp trọng tâm năm học 2026 - 2027 của ngành Giáo dục tỉnh Cao Bằng</t>
+          <t>N3_652 - Xây dựng Kế hoạch đào tạo, bồi dưỡng công chức, viên chức</t>
         </is>
       </c>
       <c r="D25" s="9" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>10/07/2026</t>
         </is>
       </c>
       <c r="E25" s="9" t="n">
@@ -1189,27 +1189,27 @@
       </c>
       <c r="H25" s="10" t="inlineStr">
         <is>
-          <t>Kế hoạch giáo dục nhà trường năm học 2026-2027</t>
+          <t>Kế hoạch số 45/KH-THPT bồi dưỡng chính trị và chuyên môn hè 2026</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B26" s="10" t="inlineStr">
         <is>
-          <t>Phê duyệt kế hoạch giáo dục của các tổ chuyên môn, tổ văn phòng và các bộ phận trong nhà trường năm học 2026 - 2027</t>
+          <t>Chỉ đạo rà soát, xét duyệt quyết toán thu chi ngân sách 6 tháng đầu năm 2026 và đối chiếu kho bạc</t>
         </is>
       </c>
       <c r="C26" s="10" t="inlineStr">
         <is>
-          <t>N3_668 - Quyết định ban hành Kế hoạch nhiệm vụ, giải pháp trọng tâm năm học 2026 - 2027 của ngành Giáo dục tỉnh Cao Bằng</t>
+          <t>N2_1158 - Xét duyệt quyết toán ngân sách Nhà nước hàng năm</t>
         </is>
       </c>
       <c r="D26" s="9" t="inlineStr">
         <is>
-          <t>18/09/2026</t>
+          <t>15/07/2026</t>
         </is>
       </c>
       <c r="E26" s="9" t="n">
@@ -1223,27 +1223,27 @@
       </c>
       <c r="H26" s="10" t="inlineStr">
         <is>
-          <t>Kế hoạch năm học các tổ TN, XH, VP đã phê duyệt</t>
+          <t>Báo cáo quyết toán tài chính ngân sách 6 tháng đầu năm 2026</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B27" s="10" t="inlineStr">
         <is>
-          <t>Chỉ đạo tổ chức thành công Hội nghị cán bộ, viên chức, người lao động năm học 2026 - 2027</t>
+          <t>Cử cán bộ quản lý, giáo viên tham gia đầy đủ các lớp tập huấn SGK, phương pháp giảng dạy và ứng dụng AI do Sở GD&amp;ĐT tổ chức</t>
         </is>
       </c>
       <c r="C27" s="10" t="inlineStr">
         <is>
-          <t>N3_668 - Quyết định ban hành Kế hoạch nhiệm vụ, giải pháp trọng tâm năm học 2026 - 2027 của ngành Giáo dục tỉnh Cao Bằng</t>
+          <t>N3_652 - Xây dựng Kế hoạch đào tạo, bồi dưỡng công chức, viên chức</t>
         </is>
       </c>
       <c r="D27" s="9" t="inlineStr">
         <is>
-          <t>28/09/2026</t>
+          <t>15/08/2026</t>
         </is>
       </c>
       <c r="E27" s="9" t="n">
@@ -1257,7 +1257,7 @@
       </c>
       <c r="H27" s="10" t="inlineStr">
         <is>
-          <t>Nghị quyết Hội nghị CBVC-NLĐ năm học 2026-2027</t>
+          <t>Quyết định cử cán bộ, giáo viên dự tập huấn hè năm 2026</t>
         </is>
       </c>
     </row>
@@ -1267,17 +1267,17 @@
       </c>
       <c r="B28" s="10" t="inlineStr">
         <is>
-          <t>Xây dựng lịch công tác tuần, tháng 9 và chương trình điều hành tổng thể hoạt động sư phạm toàn trường</t>
+          <t>Kiểm tra, nghiệm thu công tác sửa chữa phòng học, bàn ghế, hệ thống điện nước, mái che và vệ sinh khuôn viên trường trong hè</t>
         </is>
       </c>
       <c r="C28" s="10" t="inlineStr">
         <is>
-          <t>N1_610 - Chủ trì xây dựng kế hoạch, chương trình công tác của Phòng</t>
+          <t>N3_684 - Tham mưu triển khai công tác thuộc lĩnh vực Cơ sở vật chất</t>
         </is>
       </c>
       <c r="D28" s="9" t="inlineStr">
         <is>
-          <t>05/09/2026</t>
+          <t>15/08/2026</t>
         </is>
       </c>
       <c r="E28" s="9" t="n">
@@ -1291,27 +1291,27 @@
       </c>
       <c r="H28" s="10" t="inlineStr">
         <is>
-          <t>Lịch công tác tuần tháng 9/2026 đăng tải trên cổng thông tin điện tử</t>
+          <t>Biên bản nghiệm thu tu sửa cơ sở vật chất hè 2026</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B29" s="10" t="inlineStr">
         <is>
-          <t>Tổ chức họp giao ban BGH và họp Hội đồng sư phạm tháng 9/2026 đánh giá triển khai nhiệm vụ năm học mới</t>
+          <t>Rà soát, mua sắm bổ sung thiết bị dạy học tối thiểu, sách thư viện và hóa chất thí nghiệm chuẩn bị năm học mới 2026 - 2027</t>
         </is>
       </c>
       <c r="C29" s="10" t="inlineStr">
         <is>
-          <t>N1_611 - Tổ chức, điều hành, đánh giá kết quả thực hiện nhiệm vụ của công chức thuộc phòng</t>
+          <t>N3_684 - Tham mưu triển khai công tác thuộc lĩnh vực Cơ sở vật chất</t>
         </is>
       </c>
       <c r="D29" s="9" t="inlineStr">
         <is>
-          <t>15/09/2026</t>
+          <t>25/08/2026</t>
         </is>
       </c>
       <c r="E29" s="9" t="n">
@@ -1325,27 +1325,27 @@
       </c>
       <c r="H29" s="10" t="inlineStr">
         <is>
-          <t>Biên bản họp Hội đồng sư phạm tháng 9/2026</t>
+          <t>Hợp đồng mua sắm thiết bị dạy học và sách thư viện</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B30" s="10" t="inlineStr">
         <is>
-          <t>Kiểm tra, đôn đốc tiến độ thực hiện chương trình giảng dạy và nền nếp chuyên môn tháng 9</t>
+          <t>Ban hành Quyết định phân công nhiệm vụ cán bộ quản lý, phân công chuyên môn giáo viên và biên chế học sinh các lớp năm học 2026 - 2027</t>
         </is>
       </c>
       <c r="C30" s="10" t="inlineStr">
         <is>
-          <t>N1_611 - Tổ chức, điều hành, đánh giá kết quả thực hiện nhiệm vụ của công chức thuộc phòng</t>
+          <t>N1_585 - Chỉ đạo việc thực hiện các nhiệm vụ đầu năm học 2026 - 2027</t>
         </is>
       </c>
       <c r="D30" s="9" t="inlineStr">
         <is>
-          <t>30/09/2026</t>
+          <t>20/08/2026</t>
         </is>
       </c>
       <c r="E30" s="9" t="n">
@@ -1359,27 +1359,27 @@
       </c>
       <c r="H30" s="10" t="inlineStr">
         <is>
-          <t>Báo cáo kiểm tra nền nếp dạy học tháng 9/2026</t>
+          <t>Quyết định số 102/QĐ-THPT về phân công nhiệm vụ năm học 2026-2027</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B31" s="10" t="inlineStr">
         <is>
-          <t>Tổng hợp số liệu đầu năm, kiểm tra việc ổn định nền nếp dạy học tháng 9 và báo cáo Sở GD&amp;ĐT đúng thời hạn</t>
+          <t>Chỉ đạo tổ chức ngày tựu trường, đón học sinh lớp 10 và tổ chức tuần sinh hoạt tập thể đầu năm học 2026 - 2027</t>
         </is>
       </c>
       <c r="C31" s="10" t="inlineStr">
         <is>
-          <t>N2_1131 - Tổng hợp báo cáo tình hình triển khai nhiệm vụ đầu năm học 2026 - 2027</t>
+          <t>N1_585 - Chỉ đạo việc thực hiện các nhiệm vụ đầu năm học 2026 - 2027</t>
         </is>
       </c>
       <c r="D31" s="9" t="inlineStr">
         <is>
-          <t>20/09/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
       <c r="E31" s="9" t="n">
@@ -1393,27 +1393,27 @@
       </c>
       <c r="H31" s="10" t="inlineStr">
         <is>
-          <t>Báo cáo tình hình triển khai nhiệm vụ đầu năm học gửi Sở GD&amp;ĐT</t>
+          <t>Kế hoạch tựu trường và tuần sinh hoạt tập thể học sinh đầu năm</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B32" s="10" t="inlineStr">
         <is>
-          <t>Chỉ đạo triển khai công tác tuyên truyền phổ biến pháp luật, an toàn giao thông và cam kết an ninh trật tự trường học tháng 9</t>
+          <t>Xây dựng Kế hoạch và chỉ đạo tổ chức Lễ Khai giảng năm học mới 2026 - 2027 trang trọng, ý nghĩa, an toàn và tiết kiệm</t>
         </is>
       </c>
       <c r="C32" s="10" t="inlineStr">
         <is>
-          <t>N2_1131 - Tổng hợp báo cáo tình hình triển khai nhiệm vụ đầu năm học 2026 - 2027</t>
+          <t>N3_666 - Kế hoạch tham dự Lễ Khai giảng năm học 2026 - 2027 tại các cơ sở giáo dục trên địa bàn tỉnh Cao Bằng</t>
         </is>
       </c>
       <c r="D32" s="9" t="inlineStr">
         <is>
-          <t>25/09/2026</t>
+          <t>05/09/2026</t>
         </is>
       </c>
       <c r="E32" s="9" t="n">
@@ -1427,7 +1427,7 @@
       </c>
       <c r="H32" s="10" t="inlineStr">
         <is>
-          <t>Bản cam kết an toàn giao thông và phòng chống bạo lực học đường</t>
+          <t>Kế hoạch tổ chức Lễ Khai giảng năm học 2026-2027</t>
         </is>
       </c>
     </row>
@@ -1437,113 +1437,305 @@
       </c>
       <c r="B33" s="10" t="inlineStr">
         <is>
+          <t>Xây dựng và ban hành Kế hoạch giáo dục nhà trường, kế hoạch thực hiện nhiệm vụ trọng tâm năm học 2026 - 2027</t>
+        </is>
+      </c>
+      <c r="C33" s="10" t="inlineStr">
+        <is>
+          <t>N3_668 - Quyết định ban hành Kế hoạch nhiệm vụ, giải pháp trọng tâm năm học 2026 - 2027 của ngành Giáo dục tỉnh Cao Bằng</t>
+        </is>
+      </c>
+      <c r="D33" s="9" t="inlineStr">
+        <is>
+          <t>10/09/2026</t>
+        </is>
+      </c>
+      <c r="E33" s="9" t="n">
+        <v>100</v>
+      </c>
+      <c r="F33" s="9" t="n">
+        <v>100</v>
+      </c>
+      <c r="G33" s="9" t="n">
+        <v>100</v>
+      </c>
+      <c r="H33" s="10" t="inlineStr">
+        <is>
+          <t>Kế hoạch giáo dục nhà trường năm học 2026-2027</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="B34" s="10" t="inlineStr">
+        <is>
+          <t>Phê duyệt kế hoạch giáo dục của các tổ chuyên môn, tổ văn phòng và các bộ phận trong nhà trường năm học 2026 - 2027</t>
+        </is>
+      </c>
+      <c r="C34" s="10" t="inlineStr">
+        <is>
+          <t>N3_668 - Quyết định ban hành Kế hoạch nhiệm vụ, giải pháp trọng tâm năm học 2026 - 2027 của ngành Giáo dục tỉnh Cao Bằng</t>
+        </is>
+      </c>
+      <c r="D34" s="9" t="inlineStr">
+        <is>
+          <t>18/09/2026</t>
+        </is>
+      </c>
+      <c r="E34" s="9" t="n">
+        <v>100</v>
+      </c>
+      <c r="F34" s="9" t="n">
+        <v>100</v>
+      </c>
+      <c r="G34" s="9" t="n">
+        <v>100</v>
+      </c>
+      <c r="H34" s="10" t="inlineStr">
+        <is>
+          <t>Kế hoạch năm học các tổ TN, XH, VP đã phê duyệt</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="B35" s="10" t="inlineStr">
+        <is>
+          <t>Chỉ đạo tổ chức thành công Hội nghị cán bộ, viên chức, người lao động năm học 2026 - 2027</t>
+        </is>
+      </c>
+      <c r="C35" s="10" t="inlineStr">
+        <is>
+          <t>N3_668 - Quyết định ban hành Kế hoạch nhiệm vụ, giải pháp trọng tâm năm học 2026 - 2027 của ngành Giáo dục tỉnh Cao Bằng</t>
+        </is>
+      </c>
+      <c r="D35" s="9" t="inlineStr">
+        <is>
+          <t>28/09/2026</t>
+        </is>
+      </c>
+      <c r="E35" s="9" t="n">
+        <v>100</v>
+      </c>
+      <c r="F35" s="9" t="n">
+        <v>100</v>
+      </c>
+      <c r="G35" s="9" t="n">
+        <v>100</v>
+      </c>
+      <c r="H35" s="10" t="inlineStr">
+        <is>
+          <t>Nghị quyết Hội nghị CBVC-NLĐ năm học 2026-2027</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="B36" s="10" t="inlineStr">
+        <is>
+          <t>Xây dựng lịch công tác tuần, tháng 9 và chương trình điều hành tổng thể hoạt động sư phạm toàn trường</t>
+        </is>
+      </c>
+      <c r="C36" s="10" t="inlineStr">
+        <is>
+          <t>N1_610 - Chủ trì xây dựng kế hoạch, chương trình công tác của Phòng</t>
+        </is>
+      </c>
+      <c r="D36" s="9" t="inlineStr">
+        <is>
+          <t>05/09/2026</t>
+        </is>
+      </c>
+      <c r="E36" s="9" t="n">
+        <v>100</v>
+      </c>
+      <c r="F36" s="9" t="n">
+        <v>100</v>
+      </c>
+      <c r="G36" s="9" t="n">
+        <v>100</v>
+      </c>
+      <c r="H36" s="10" t="inlineStr">
+        <is>
+          <t>Lịch công tác tuần tháng 9/2026 đăng tải trên cổng thông tin điện tử</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="B37" s="10" t="inlineStr">
+        <is>
+          <t>Tổ chức họp giao ban BGH và họp Hội đồng sư phạm tháng 9/2026 đánh giá triển khai nhiệm vụ năm học mới</t>
+        </is>
+      </c>
+      <c r="C37" s="10" t="inlineStr">
+        <is>
+          <t>N1_611 - Tổ chức, điều hành, đánh giá kết quả thực hiện nhiệm vụ của công chức thuộc phòng</t>
+        </is>
+      </c>
+      <c r="D37" s="9" t="inlineStr">
+        <is>
+          <t>15/09/2026</t>
+        </is>
+      </c>
+      <c r="E37" s="9" t="n">
+        <v>100</v>
+      </c>
+      <c r="F37" s="9" t="n">
+        <v>100</v>
+      </c>
+      <c r="G37" s="9" t="n">
+        <v>100</v>
+      </c>
+      <c r="H37" s="10" t="inlineStr">
+        <is>
+          <t>Biên bản họp Hội đồng sư phạm tháng 9/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="B38" s="10" t="inlineStr">
+        <is>
+          <t>Kiểm tra, đôn đốc tiến độ thực hiện chương trình giảng dạy và nền nếp chuyên môn tháng 9</t>
+        </is>
+      </c>
+      <c r="C38" s="10" t="inlineStr">
+        <is>
+          <t>N1_611 - Tổ chức, điều hành, đánh giá kết quả thực hiện nhiệm vụ của công chức thuộc phòng</t>
+        </is>
+      </c>
+      <c r="D38" s="9" t="inlineStr">
+        <is>
+          <t>30/09/2026</t>
+        </is>
+      </c>
+      <c r="E38" s="9" t="n">
+        <v>100</v>
+      </c>
+      <c r="F38" s="9" t="n">
+        <v>100</v>
+      </c>
+      <c r="G38" s="9" t="n">
+        <v>100</v>
+      </c>
+      <c r="H38" s="10" t="inlineStr">
+        <is>
+          <t>Báo cáo kiểm tra nền nếp dạy học tháng 9/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="B39" s="10" t="inlineStr">
+        <is>
+          <t>Tổng hợp số liệu đầu năm, kiểm tra việc ổn định nền nếp dạy học tháng 9 và báo cáo Sở GD&amp;ĐT đúng thời hạn</t>
+        </is>
+      </c>
+      <c r="C39" s="10" t="inlineStr">
+        <is>
+          <t>N2_1131 - Tổng hợp báo cáo tình hình triển khai nhiệm vụ đầu năm học 2026 - 2027</t>
+        </is>
+      </c>
+      <c r="D39" s="9" t="inlineStr">
+        <is>
+          <t>20/09/2026</t>
+        </is>
+      </c>
+      <c r="E39" s="9" t="n">
+        <v>100</v>
+      </c>
+      <c r="F39" s="9" t="n">
+        <v>100</v>
+      </c>
+      <c r="G39" s="9" t="n">
+        <v>100</v>
+      </c>
+      <c r="H39" s="10" t="inlineStr">
+        <is>
+          <t>Báo cáo tình hình triển khai nhiệm vụ đầu năm học gửi Sở GD&amp;ĐT</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="B40" s="10" t="inlineStr">
+        <is>
+          <t>Chỉ đạo triển khai công tác tuyên truyền phổ biến pháp luật, an toàn giao thông và cam kết an ninh trật tự trường học tháng 9</t>
+        </is>
+      </c>
+      <c r="C40" s="10" t="inlineStr">
+        <is>
+          <t>N2_1131 - Tổng hợp báo cáo tình hình triển khai nhiệm vụ đầu năm học 2026 - 2027</t>
+        </is>
+      </c>
+      <c r="D40" s="9" t="inlineStr">
+        <is>
+          <t>25/09/2026</t>
+        </is>
+      </c>
+      <c r="E40" s="9" t="n">
+        <v>100</v>
+      </c>
+      <c r="F40" s="9" t="n">
+        <v>100</v>
+      </c>
+      <c r="G40" s="9" t="n">
+        <v>100</v>
+      </c>
+      <c r="H40" s="10" t="inlineStr">
+        <is>
+          <t>Bản cam kết an toàn giao thông và phòng chống bạo lực học đường</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="B41" s="10" t="inlineStr">
+        <is>
           <t>Ban hành Thông báo Lịch tiếp công dân năm học 2026 - 2027; tiếp nhận và giải quyết kịp thời phản ánh của phụ huynh đầu năm học</t>
         </is>
       </c>
-      <c r="C33" s="10" t="inlineStr">
+      <c r="C41" s="10" t="inlineStr">
         <is>
           <t>N1_572 - Tiếp công dân định kỳ cùng Giám đốc Sở GDĐT</t>
         </is>
       </c>
-      <c r="D33" s="9" t="inlineStr">
+      <c r="D41" s="9" t="inlineStr">
         <is>
           <t>15/09/2026</t>
         </is>
       </c>
-      <c r="E33" s="9" t="n">
-        <v>100</v>
-      </c>
-      <c r="F33" s="9" t="n">
-        <v>100</v>
-      </c>
-      <c r="G33" s="9" t="n">
-        <v>100</v>
-      </c>
-      <c r="H33" s="10" t="inlineStr">
+      <c r="E41" s="9" t="n">
+        <v>100</v>
+      </c>
+      <c r="F41" s="9" t="n">
+        <v>100</v>
+      </c>
+      <c r="G41" s="9" t="n">
+        <v>100</v>
+      </c>
+      <c r="H41" s="10" t="inlineStr">
         <is>
           <t>Thông báo lịch tiếp công dân năm học 2026-2027 và sổ tiếp dân</t>
         </is>
       </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="9" t="n"/>
-      <c r="B34" s="10" t="n"/>
-      <c r="C34" s="10" t="n"/>
-      <c r="D34" s="9" t="n"/>
-      <c r="E34" s="9" t="n"/>
-      <c r="F34" s="9" t="n"/>
-      <c r="G34" s="9" t="n"/>
-      <c r="H34" s="10" t="n"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="9" t="n"/>
-      <c r="B35" s="10" t="n"/>
-      <c r="C35" s="10" t="n"/>
-      <c r="D35" s="9" t="n"/>
-      <c r="E35" s="9" t="n"/>
-      <c r="F35" s="9" t="n"/>
-      <c r="G35" s="9" t="n"/>
-      <c r="H35" s="10" t="n"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="9" t="n"/>
-      <c r="B36" s="10" t="n"/>
-      <c r="C36" s="10" t="n"/>
-      <c r="D36" s="9" t="n"/>
-      <c r="E36" s="9" t="n"/>
-      <c r="F36" s="9" t="n"/>
-      <c r="G36" s="9" t="n"/>
-      <c r="H36" s="10" t="n"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="9" t="n"/>
-      <c r="B37" s="10" t="n"/>
-      <c r="C37" s="10" t="n"/>
-      <c r="D37" s="9" t="n"/>
-      <c r="E37" s="9" t="n"/>
-      <c r="F37" s="9" t="n"/>
-      <c r="G37" s="9" t="n"/>
-      <c r="H37" s="10" t="n"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="9" t="n"/>
-      <c r="B38" s="10" t="n"/>
-      <c r="C38" s="10" t="n"/>
-      <c r="D38" s="9" t="n"/>
-      <c r="E38" s="9" t="n"/>
-      <c r="F38" s="9" t="n"/>
-      <c r="G38" s="9" t="n"/>
-      <c r="H38" s="10" t="n"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="9" t="n"/>
-      <c r="B39" s="10" t="n"/>
-      <c r="C39" s="10" t="n"/>
-      <c r="D39" s="9" t="n"/>
-      <c r="E39" s="9" t="n"/>
-      <c r="F39" s="9" t="n"/>
-      <c r="G39" s="9" t="n"/>
-      <c r="H39" s="10" t="n"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="9" t="n"/>
-      <c r="B40" s="10" t="n"/>
-      <c r="C40" s="10" t="n"/>
-      <c r="D40" s="9" t="n"/>
-      <c r="E40" s="9" t="n"/>
-      <c r="F40" s="9" t="n"/>
-      <c r="G40" s="9" t="n"/>
-      <c r="H40" s="10" t="n"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="9" t="n"/>
-      <c r="B41" s="10" t="n"/>
-      <c r="C41" s="10" t="n"/>
-      <c r="D41" s="9" t="n"/>
-      <c r="E41" s="9" t="n"/>
-      <c r="F41" s="9" t="n"/>
-      <c r="G41" s="9" t="n"/>
-      <c r="H41" s="10" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="9" t="n"/>
@@ -1885,6 +2077,337 @@
       <c r="G75" s="9" t="n"/>
       <c r="H75" s="10" t="n"/>
     </row>
+    <row r="76">
+      <c r="A76" s="9" t="n"/>
+      <c r="B76" s="10" t="n"/>
+      <c r="C76" s="10" t="n"/>
+      <c r="D76" s="9" t="n"/>
+      <c r="E76" s="9" t="n"/>
+      <c r="F76" s="9" t="n"/>
+      <c r="G76" s="9" t="n"/>
+      <c r="H76" s="10" t="n"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="9" t="n"/>
+      <c r="B77" s="10" t="n"/>
+      <c r="C77" s="10" t="n"/>
+      <c r="D77" s="9" t="n"/>
+      <c r="E77" s="9" t="n"/>
+      <c r="F77" s="9" t="n"/>
+      <c r="G77" s="9" t="n"/>
+      <c r="H77" s="10" t="n"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="9" t="n"/>
+      <c r="B78" s="10" t="n"/>
+      <c r="C78" s="10" t="n"/>
+      <c r="D78" s="9" t="n"/>
+      <c r="E78" s="9" t="n"/>
+      <c r="F78" s="9" t="n"/>
+      <c r="G78" s="9" t="n"/>
+      <c r="H78" s="10" t="n"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="9" t="n"/>
+      <c r="B79" s="10" t="n"/>
+      <c r="C79" s="10" t="n"/>
+      <c r="D79" s="9" t="n"/>
+      <c r="E79" s="9" t="n"/>
+      <c r="F79" s="9" t="n"/>
+      <c r="G79" s="9" t="n"/>
+      <c r="H79" s="10" t="n"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="9" t="n"/>
+      <c r="B80" s="10" t="n"/>
+      <c r="C80" s="10" t="n"/>
+      <c r="D80" s="9" t="n"/>
+      <c r="E80" s="9" t="n"/>
+      <c r="F80" s="9" t="n"/>
+      <c r="G80" s="9" t="n"/>
+      <c r="H80" s="10" t="n"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="9" t="n"/>
+      <c r="B81" s="10" t="n"/>
+      <c r="C81" s="10" t="n"/>
+      <c r="D81" s="9" t="n"/>
+      <c r="E81" s="9" t="n"/>
+      <c r="F81" s="9" t="n"/>
+      <c r="G81" s="9" t="n"/>
+      <c r="H81" s="10" t="n"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="9" t="n"/>
+      <c r="B82" s="10" t="n"/>
+      <c r="C82" s="10" t="n"/>
+      <c r="D82" s="9" t="n"/>
+      <c r="E82" s="9" t="n"/>
+      <c r="F82" s="9" t="n"/>
+      <c r="G82" s="9" t="n"/>
+      <c r="H82" s="10" t="n"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="9" t="n"/>
+      <c r="B83" s="10" t="n"/>
+      <c r="C83" s="10" t="n"/>
+      <c r="D83" s="9" t="n"/>
+      <c r="E83" s="9" t="n"/>
+      <c r="F83" s="9" t="n"/>
+      <c r="G83" s="9" t="n"/>
+      <c r="H83" s="10" t="n"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="9" t="n"/>
+      <c r="B84" s="10" t="n"/>
+      <c r="C84" s="10" t="n"/>
+      <c r="D84" s="9" t="n"/>
+      <c r="E84" s="9" t="n"/>
+      <c r="F84" s="9" t="n"/>
+      <c r="G84" s="9" t="n"/>
+      <c r="H84" s="10" t="n"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="9" t="n"/>
+      <c r="B85" s="10" t="n"/>
+      <c r="C85" s="10" t="n"/>
+      <c r="D85" s="9" t="n"/>
+      <c r="E85" s="9" t="n"/>
+      <c r="F85" s="9" t="n"/>
+      <c r="G85" s="9" t="n"/>
+      <c r="H85" s="10" t="n"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="9" t="n"/>
+      <c r="B86" s="10" t="n"/>
+      <c r="C86" s="10" t="n"/>
+      <c r="D86" s="9" t="n"/>
+      <c r="E86" s="9" t="n"/>
+      <c r="F86" s="9" t="n"/>
+      <c r="G86" s="9" t="n"/>
+      <c r="H86" s="10" t="n"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="9" t="n"/>
+      <c r="B87" s="10" t="n"/>
+      <c r="C87" s="10" t="n"/>
+      <c r="D87" s="9" t="n"/>
+      <c r="E87" s="9" t="n"/>
+      <c r="F87" s="9" t="n"/>
+      <c r="G87" s="9" t="n"/>
+      <c r="H87" s="10" t="n"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="9" t="n"/>
+      <c r="B88" s="10" t="n"/>
+      <c r="C88" s="10" t="n"/>
+      <c r="D88" s="9" t="n"/>
+      <c r="E88" s="9" t="n"/>
+      <c r="F88" s="9" t="n"/>
+      <c r="G88" s="9" t="n"/>
+      <c r="H88" s="10" t="n"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="9" t="n"/>
+      <c r="B89" s="10" t="n"/>
+      <c r="C89" s="10" t="n"/>
+      <c r="D89" s="9" t="n"/>
+      <c r="E89" s="9" t="n"/>
+      <c r="F89" s="9" t="n"/>
+      <c r="G89" s="9" t="n"/>
+      <c r="H89" s="10" t="n"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="9" t="n"/>
+      <c r="B90" s="10" t="n"/>
+      <c r="C90" s="10" t="n"/>
+      <c r="D90" s="9" t="n"/>
+      <c r="E90" s="9" t="n"/>
+      <c r="F90" s="9" t="n"/>
+      <c r="G90" s="9" t="n"/>
+      <c r="H90" s="10" t="n"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="9" t="n"/>
+      <c r="B91" s="10" t="n"/>
+      <c r="C91" s="10" t="n"/>
+      <c r="D91" s="9" t="n"/>
+      <c r="E91" s="9" t="n"/>
+      <c r="F91" s="9" t="n"/>
+      <c r="G91" s="9" t="n"/>
+      <c r="H91" s="10" t="n"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="9" t="n"/>
+      <c r="B92" s="10" t="n"/>
+      <c r="C92" s="10" t="n"/>
+      <c r="D92" s="9" t="n"/>
+      <c r="E92" s="9" t="n"/>
+      <c r="F92" s="9" t="n"/>
+      <c r="G92" s="9" t="n"/>
+      <c r="H92" s="10" t="n"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="9" t="n"/>
+      <c r="B93" s="10" t="n"/>
+      <c r="C93" s="10" t="n"/>
+      <c r="D93" s="9" t="n"/>
+      <c r="E93" s="9" t="n"/>
+      <c r="F93" s="9" t="n"/>
+      <c r="G93" s="9" t="n"/>
+      <c r="H93" s="10" t="n"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="9" t="n"/>
+      <c r="B94" s="10" t="n"/>
+      <c r="C94" s="10" t="n"/>
+      <c r="D94" s="9" t="n"/>
+      <c r="E94" s="9" t="n"/>
+      <c r="F94" s="9" t="n"/>
+      <c r="G94" s="9" t="n"/>
+      <c r="H94" s="10" t="n"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="9" t="n"/>
+      <c r="B95" s="10" t="n"/>
+      <c r="C95" s="10" t="n"/>
+      <c r="D95" s="9" t="n"/>
+      <c r="E95" s="9" t="n"/>
+      <c r="F95" s="9" t="n"/>
+      <c r="G95" s="9" t="n"/>
+      <c r="H95" s="10" t="n"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="9" t="n"/>
+      <c r="B96" s="10" t="n"/>
+      <c r="C96" s="10" t="n"/>
+      <c r="D96" s="9" t="n"/>
+      <c r="E96" s="9" t="n"/>
+      <c r="F96" s="9" t="n"/>
+      <c r="G96" s="9" t="n"/>
+      <c r="H96" s="10" t="n"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="9" t="n"/>
+      <c r="B97" s="10" t="n"/>
+      <c r="C97" s="10" t="n"/>
+      <c r="D97" s="9" t="n"/>
+      <c r="E97" s="9" t="n"/>
+      <c r="F97" s="9" t="n"/>
+      <c r="G97" s="9" t="n"/>
+      <c r="H97" s="10" t="n"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="9" t="n"/>
+      <c r="B98" s="10" t="n"/>
+      <c r="C98" s="10" t="n"/>
+      <c r="D98" s="9" t="n"/>
+      <c r="E98" s="9" t="n"/>
+      <c r="F98" s="9" t="n"/>
+      <c r="G98" s="9" t="n"/>
+      <c r="H98" s="10" t="n"/>
+    </row>
+    <row r="99"/>
+    <row r="100"/>
+    <row r="101"/>
+    <row r="102"/>
+    <row r="103"/>
+    <row r="104"/>
+    <row r="105"/>
+    <row r="106"/>
+    <row r="107"/>
+    <row r="108"/>
+    <row r="109"/>
+    <row r="110"/>
+    <row r="111"/>
+    <row r="112"/>
+    <row r="113"/>
+    <row r="114"/>
+    <row r="115"/>
+    <row r="116"/>
+    <row r="117"/>
+    <row r="118"/>
+    <row r="119"/>
+    <row r="120"/>
+    <row r="121"/>
+    <row r="122"/>
+    <row r="123"/>
+    <row r="124"/>
+    <row r="125"/>
+    <row r="126"/>
+    <row r="127"/>
+    <row r="128"/>
+    <row r="129"/>
+    <row r="130"/>
+    <row r="131"/>
+    <row r="132"/>
+    <row r="133"/>
+    <row r="134"/>
+    <row r="135"/>
+    <row r="136"/>
+    <row r="137"/>
+    <row r="138"/>
+    <row r="139"/>
+    <row r="140"/>
+    <row r="141"/>
+    <row r="142"/>
+    <row r="143"/>
+    <row r="144"/>
+    <row r="145"/>
+    <row r="146"/>
+    <row r="147"/>
+    <row r="148"/>
+    <row r="149"/>
+    <row r="150"/>
+    <row r="151"/>
+    <row r="152"/>
+    <row r="153"/>
+    <row r="154"/>
+    <row r="155"/>
+    <row r="156"/>
+    <row r="157"/>
+    <row r="158"/>
+    <row r="159"/>
+    <row r="160"/>
+    <row r="161"/>
+    <row r="162"/>
+    <row r="163"/>
+    <row r="164"/>
+    <row r="165"/>
+    <row r="166"/>
+    <row r="167"/>
+    <row r="168"/>
+    <row r="169"/>
+    <row r="170"/>
+    <row r="171"/>
+    <row r="172"/>
+    <row r="173"/>
+    <row r="174"/>
+    <row r="175"/>
+    <row r="176"/>
+    <row r="177"/>
+    <row r="178"/>
+    <row r="179"/>
+    <row r="180"/>
+    <row r="181"/>
+    <row r="182"/>
+    <row r="183"/>
+    <row r="184"/>
+    <row r="185"/>
+    <row r="186"/>
+    <row r="187"/>
+    <row r="188"/>
+    <row r="189"/>
+    <row r="190"/>
+    <row r="191"/>
+    <row r="192"/>
+    <row r="193"/>
+    <row r="194"/>
+    <row r="195"/>
+    <row r="196"/>
+    <row r="197"/>
+    <row r="198"/>
+    <row r="199"/>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="A2:L2"/>
